--- a/public/templates/JobLine_Setup_Template.xlsx
+++ b/public/templates/JobLine_Setup_Template.xlsx
@@ -1,51 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <bookViews>
-    <workbookView firstSheet="5" activeTab="7" tabRatio="500"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet r:id="rId1" name="Instructions" sheetId="1"/>
-    <sheet r:id="rId2" name="Teams" sheetId="2"/>
-    <sheet r:id="rId3" name="Departments" sheetId="3"/>
-    <sheet r:id="rId4" name="Stations" sheetId="4"/>
-    <sheet r:id="rId5" name="Stations - Valid Values" sheetId="5"/>
-    <sheet r:id="rId6" name="Users" sheetId="6"/>
-    <sheet r:id="rId7" name="Users - Valid Values" sheetId="7"/>
-    <sheet r:id="rId8" name="Work Orders" sheetId="8"/>
-    <sheet r:id="rId9" name="Work Orders - Valid Values" sheetId="9"/>
-    <sheet r:id="rId10" name="Routing Templates" sheetId="10"/>
-    <sheet r:id="rId11" name="Routing Templates - Valid Values" sheetId="11"/>
+    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Teams" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Departments" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Stations" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Stations - Valid Values" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Users" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Users - Valid Values" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Work Orders" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Work Orders - Valid Values" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Routing Templates" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Routing Templates - Valid" state="visible" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="0" iterateCount="100" iterateDelta="0.001"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="D8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[?] No 'Saw' Work Center Type in valid values list. Used 'Press Brake' as placeholder - update to correct type if available.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="343">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -305,7 +281,7 @@
     <t>Step type (quote, engineering, internal, etc.)</t>
   </si>
   <si>
-    <t>Physical area where step is performed (must match a Station Work Center)</t>
+    <t>Physical area where step is performed</t>
   </si>
   <si>
     <t>Est. Duration (min)</t>
@@ -416,18 +392,12 @@
     <t>Description (optional)</t>
   </si>
   <si>
-    <t>Team Valid?</t>
-  </si>
-  <si>
     <t>Machining</t>
   </si>
   <si>
     <t>CNC milling and lathe operations</t>
   </si>
   <si>
-    <t>✓</t>
-  </si>
-  <si>
     <t>Machining - Night</t>
   </si>
   <si>
@@ -689,7 +659,7 @@
     <t>Hardware Installation</t>
   </si>
   <si>
-    <t>CNC Mill, CNC Lathe, Water Jet, Band Saw, Press Brake, TIG Welding, MIG Welding, Electron Beam Welding, Punch Press, Hardware Installation, Deburr Station, Shipping, Incoming Inspection, Outgoing Inspection, Tool Crib, Quoting, Engineering Review, CAM Programming, Purchasing, Receiving, Final Inspection, Grinding</t>
+    <t>CNC Mill, CNC Lathe, Water Jet, Band Saw, Press Brake, TIG Welding, MIG Welding, Electron Beam Welding, Punch Press, Hardware Installation, Deburr Station, Shipping, Incoming Inspection, Outgoing Inspection, Final Inspection, Tool Crib, Quoting, Engineering Review, CAM Programming, Purchasing, Receiving, Grinding</t>
   </si>
   <si>
     <t>Org Role (optional)</t>
@@ -764,9 +734,6 @@
     <t>Tags (comma-separated)</t>
   </si>
   <si>
-    <t>Station Valid?</t>
-  </si>
-  <si>
     <t>WO-2026-001</t>
   </si>
   <si>
@@ -779,6 +746,9 @@
     <t>10</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
     <t>normal</t>
   </si>
   <si>
@@ -788,6 +758,9 @@
     <t>2026-03-15</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>rush,aerospace</t>
   </si>
   <si>
@@ -806,6 +779,9 @@
     <t>20</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>high</t>
   </si>
   <si>
@@ -815,6 +791,9 @@
     <t>2026-03-12</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>priority</t>
   </si>
   <si>
@@ -833,9 +812,15 @@
     <t>30</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
     <t>2026-03-20</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>Final inspection of cover plates</t>
   </si>
   <si>
@@ -857,6 +842,9 @@
     <t>2026-03-10</t>
   </si>
   <si>
+    <t>180</t>
+  </si>
+  <si>
     <t>hot-job,customer-urgent</t>
   </si>
   <si>
@@ -872,6 +860,9 @@
     <t>FRM-7890</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>critical</t>
   </si>
   <si>
@@ -881,6 +872,9 @@
     <t>2026-03-08</t>
   </si>
   <si>
+    <t>480</t>
+  </si>
+  <si>
     <t>prototype,engineering</t>
   </si>
   <si>
@@ -893,6 +887,9 @@
     <t>PART-*</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>Quote Review &amp; Approval</t>
   </si>
   <si>
@@ -908,12 +905,18 @@
     <t>Review drawings, tolerances, and material specs</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Programming/CAM</t>
   </si>
   <si>
     <t>Create CNC programs and toolpaths</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>Materials Purchasing</t>
   </si>
   <si>
@@ -923,21 +926,33 @@
     <t>Order raw materials and special tooling</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>Materials Receiving</t>
   </si>
   <si>
     <t>receiving</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Receive and verify material certifications</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>inspection</t>
   </si>
   <si>
     <t>Verify material dimensions and condition</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>Material Cutting/Prep</t>
   </si>
   <si>
@@ -947,15 +962,27 @@
     <t>Cut material to rough size</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>Tool Setup &amp; Prep</t>
   </si>
   <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>Pull and verify tooling, fixtures, and gages</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>First Article Setup</t>
   </si>
   <si>
+    <t>90</t>
+  </si>
+  <si>
     <t>Setup machine and run first article</t>
   </si>
   <si>
@@ -965,18 +992,27 @@
     <t>Full dimensional inspection per drawing</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>Production Run</t>
   </si>
   <si>
     <t>Complete production quantity</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>Deburr/Finish</t>
   </si>
   <si>
     <t>Remove burrs and clean parts</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>Heat Treat</t>
   </si>
   <si>
@@ -989,6 +1025,9 @@
     <t>HRC 58-62 per spec</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>Final QC check before shipping</t>
   </si>
   <si>
@@ -996,6 +1035,9 @@
   </si>
   <si>
     <t>Package per customer requirements</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>Ship to Customer</t>
@@ -1013,34 +1055,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="421" formatCode="yyyy-mm-dd"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <i val="0"/>
-      <color auto="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <color auto="1"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1056,13 +1081,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1072,25 +1091,26 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0"/>
-    <xf numFmtId="421" fontId="2" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1239,20 +1259,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1374,23 +1390,63 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{40DD0128-AE58-B4BB-C748-8FFA9BD996E8}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10011"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="18.00390625" customWidth="1"/>
-    <col min="3" max="3" width="10.00390625" customWidth="1"/>
-    <col min="4" max="4" width="39.00390625" customWidth="1"/>
-    <col min="5" max="5" width="50.00390625" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="39" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1407,7 +1463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1424,7 +1480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1441,7 +1497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1458,7 +1514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1475,7 +1531,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1492,7 +1548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1509,7 +1565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1526,7 +1582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1543,7 +1599,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1560,7 +1616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1577,7 +1633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1594,7 +1650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1611,7 +1667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1628,7 +1684,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1645,7 +1701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1662,7 +1718,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1679,7 +1735,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1696,7 +1752,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1713,7 +1769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1730,7 +1786,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -1747,7 +1803,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -1764,7 +1820,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1781,7 +1837,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1798,7 +1854,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -1815,7 +1871,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -1832,7 +1888,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1849,7 +1905,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -1866,7 +1922,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -1883,7 +1939,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>50</v>
       </c>
@@ -1900,7 +1956,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1917,7 +1973,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1934,7 +1990,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1951,7 +2007,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -1968,7 +2024,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -1985,7 +2041,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2002,7 +2058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2019,7 +2075,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -2036,7 +2092,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -2053,7 +2109,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -2070,7 +2126,24 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>75</v>
       </c>
@@ -2080,11 +2153,14 @@
       <c r="C42" t="s">
         <v>10</v>
       </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
       <c r="E42" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>75</v>
       </c>
@@ -2094,11 +2170,14 @@
       <c r="C43" t="s">
         <v>10</v>
       </c>
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
       <c r="E43" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -2108,11 +2187,14 @@
       <c r="C44" t="s">
         <v>10</v>
       </c>
+      <c r="D44" t="s">
+        <v>6</v>
+      </c>
       <c r="E44" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>75</v>
       </c>
@@ -2122,11 +2204,14 @@
       <c r="C45" t="s">
         <v>10</v>
       </c>
+      <c r="D45" t="s">
+        <v>6</v>
+      </c>
       <c r="E45" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>75</v>
       </c>
@@ -2143,7 +2228,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2153,11 +2238,14 @@
       <c r="C47" t="s">
         <v>12</v>
       </c>
+      <c r="D47" t="s">
+        <v>6</v>
+      </c>
       <c r="E47" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -2167,11 +2255,14 @@
       <c r="C48" t="s">
         <v>12</v>
       </c>
+      <c r="D48" t="s">
+        <v>6</v>
+      </c>
       <c r="E48" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>75</v>
       </c>
@@ -2181,11 +2272,14 @@
       <c r="C49" t="s">
         <v>12</v>
       </c>
+      <c r="D49" t="s">
+        <v>6</v>
+      </c>
       <c r="E49" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -2195,13 +2289,33 @@
       <c r="C50" t="s">
         <v>12</v>
       </c>
+      <c r="D50" t="s">
+        <v>6</v>
+      </c>
       <c r="E50" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="B52" t="s">
         <v>6</v>
@@ -2213,15 +2327,15 @@
         <v>6</v>
       </c>
       <c r="E52" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" ht="16.5" customHeight="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
         <v>6</v>
@@ -2230,15 +2344,15 @@
         <v>6</v>
       </c>
       <c r="E53" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" ht="16.5" customHeight="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s">
         <v>6</v>
@@ -2247,15 +2361,15 @@
         <v>6</v>
       </c>
       <c r="E54" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55" ht="16.5" customHeight="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C55" t="s">
         <v>6</v>
@@ -2264,15 +2378,15 @@
         <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="56" ht="16.5" customHeight="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C56" t="s">
         <v>6</v>
@@ -2281,15 +2395,15 @@
         <v>6</v>
       </c>
       <c r="E56" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" ht="16.5" customHeight="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C57" t="s">
         <v>6</v>
@@ -2298,15 +2412,15 @@
         <v>6</v>
       </c>
       <c r="E57" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" ht="16.5" customHeight="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C58" t="s">
         <v>6</v>
@@ -2315,44 +2429,30 @@
         <v>6</v>
       </c>
       <c r="E58" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" ht="16.5" customHeight="1">
-      <c r="B59" t="s">
-        <v>105</v>
-      </c>
-      <c r="E59" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7816D128-D1F8-80B8-2DDE-4730D4F9CCB4}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24.00390625" customWidth="1"/>
-    <col min="2" max="2" width="21.00390625" customWidth="1"/>
-    <col min="3" max="3" width="8.00390625" customWidth="1"/>
-    <col min="4" max="4" width="26.00390625" customWidth="1"/>
-    <col min="5" max="5" width="20.00390625" customWidth="1"/>
-    <col min="6" max="8" width="21.00390625" customWidth="1"/>
-    <col min="9" max="9" width="49.00390625" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="6" width="20" customWidth="1"/>
+    <col min="7" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>76</v>
       </c>
@@ -2381,535 +2481,518 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+        <v>287</v>
+      </c>
+      <c r="C2" t="s">
+        <v>288</v>
       </c>
       <c r="D2" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" t="s">
+        <v>245</v>
+      </c>
+      <c r="H4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E5" t="s">
+        <v>299</v>
+      </c>
+      <c r="F5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G5" t="s">
+        <v>262</v>
+      </c>
+      <c r="H5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C6" t="s">
+        <v>301</v>
+      </c>
+      <c r="D6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" t="s">
+        <v>304</v>
+      </c>
+      <c r="H6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" t="s">
+        <v>307</v>
+      </c>
+      <c r="F7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D8" t="s">
+        <v>310</v>
+      </c>
+      <c r="E8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" t="s">
+        <v>262</v>
+      </c>
+      <c r="H8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" t="s">
+        <v>314</v>
+      </c>
+      <c r="E9" t="s">
+        <v>311</v>
+      </c>
+      <c r="F9" t="s">
+        <v>200</v>
+      </c>
+      <c r="G9" t="s">
+        <v>315</v>
+      </c>
+      <c r="H9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" t="s">
+        <v>317</v>
+      </c>
+      <c r="D10" t="s">
+        <v>318</v>
+      </c>
+      <c r="E10" t="s">
+        <v>311</v>
+      </c>
+      <c r="F10" t="s">
+        <v>146</v>
+      </c>
+      <c r="G10" t="s">
+        <v>319</v>
+      </c>
+      <c r="H10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" t="s">
+        <v>321</v>
+      </c>
+      <c r="E11" t="s">
+        <v>307</v>
+      </c>
+      <c r="F11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G11" t="s">
+        <v>265</v>
+      </c>
+      <c r="H11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D12" t="s">
+        <v>324</v>
+      </c>
+      <c r="E12" t="s">
+        <v>311</v>
+      </c>
+      <c r="F12" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" t="s">
+        <v>256</v>
+      </c>
+      <c r="H12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>286</v>
+      </c>
+      <c r="B13" t="s">
+        <v>287</v>
+      </c>
+      <c r="C13" t="s">
+        <v>326</v>
+      </c>
+      <c r="D13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E13" t="s">
+        <v>311</v>
+      </c>
+      <c r="F13" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" t="s">
+        <v>262</v>
+      </c>
+      <c r="H13" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C14" t="s">
+        <v>329</v>
+      </c>
+      <c r="D14" t="s">
+        <v>330</v>
+      </c>
+      <c r="E14" t="s">
+        <v>331</v>
+      </c>
+      <c r="F14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" t="s">
         <v>283</v>
       </c>
-      <c r="F2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G2">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E3" t="s">
-        <v>285</v>
-      </c>
-      <c r="F3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G3">
-        <v>60</v>
-      </c>
-      <c r="H3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="H14" t="s">
+        <v>332</v>
+      </c>
+      <c r="I14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B15" t="s">
         <v>287</v>
       </c>
-      <c r="E4" t="s">
-        <v>285</v>
-      </c>
-      <c r="F4" t="s">
-        <v>188</v>
-      </c>
-      <c r="G4">
-        <v>120</v>
-      </c>
-      <c r="H4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>289</v>
-      </c>
-      <c r="E5" t="s">
-        <v>290</v>
-      </c>
-      <c r="F5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G5">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" t="s">
-        <v>281</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E6" t="s">
-        <v>293</v>
-      </c>
-      <c r="F6" t="s">
-        <v>198</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" t="s">
-        <v>280</v>
-      </c>
-      <c r="B7" t="s">
-        <v>281</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E7" t="s">
-        <v>295</v>
-      </c>
-      <c r="F7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G7">
-        <v>30</v>
-      </c>
-      <c r="H7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" t="s">
-        <v>280</v>
-      </c>
-      <c r="B8" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>297</v>
-      </c>
-      <c r="E8" t="s">
-        <v>298</v>
-      </c>
-      <c r="F8" t="s">
-        <v>159</v>
-      </c>
-      <c r="G8">
-        <v>30</v>
-      </c>
-      <c r="H8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" t="s">
-        <v>280</v>
-      </c>
-      <c r="B9" t="s">
-        <v>281</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>300</v>
-      </c>
-      <c r="E9" t="s">
-        <v>298</v>
-      </c>
-      <c r="F9" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9">
-        <v>45</v>
-      </c>
-      <c r="H9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" t="s">
-        <v>280</v>
-      </c>
-      <c r="B10" t="s">
-        <v>281</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>302</v>
-      </c>
-      <c r="E10" t="s">
-        <v>298</v>
-      </c>
-      <c r="F10" t="s">
-        <v>148</v>
-      </c>
-      <c r="G10">
-        <v>90</v>
-      </c>
-      <c r="H10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" t="s">
-        <v>280</v>
-      </c>
-      <c r="B11" t="s">
-        <v>281</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C15" t="s">
+        <v>334</v>
+      </c>
+      <c r="D15" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" t="s">
+        <v>307</v>
+      </c>
+      <c r="F15" t="s">
+        <v>165</v>
+      </c>
+      <c r="G15" t="s">
+        <v>262</v>
+      </c>
+      <c r="H15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>286</v>
+      </c>
+      <c r="B16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C16" t="s">
         <v>304</v>
       </c>
-      <c r="E11" t="s">
-        <v>295</v>
-      </c>
-      <c r="F11" t="s">
-        <v>167</v>
-      </c>
-      <c r="G11">
-        <v>60</v>
-      </c>
-      <c r="H11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" t="s">
-        <v>280</v>
-      </c>
-      <c r="B12" t="s">
-        <v>281</v>
-      </c>
-      <c r="C12">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>306</v>
-      </c>
-      <c r="E12" t="s">
-        <v>298</v>
-      </c>
-      <c r="F12" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12">
-        <v>240</v>
-      </c>
-      <c r="H12" t="s">
-        <v>6</v>
-      </c>
-      <c r="I12" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" t="s">
-        <v>280</v>
-      </c>
-      <c r="B13" t="s">
-        <v>281</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>308</v>
-      </c>
-      <c r="E13" t="s">
-        <v>298</v>
-      </c>
-      <c r="F13" t="s">
-        <v>174</v>
-      </c>
-      <c r="G13">
-        <v>30</v>
-      </c>
-      <c r="H13" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" t="s">
-        <v>280</v>
-      </c>
-      <c r="B14" t="s">
-        <v>281</v>
-      </c>
-      <c r="C14">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>310</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D16" t="s">
+        <v>336</v>
+      </c>
+      <c r="E16" t="s">
         <v>311</v>
       </c>
-      <c r="F14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14">
-        <v>480</v>
-      </c>
-      <c r="H14" t="s">
-        <v>312</v>
-      </c>
-      <c r="I14" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" t="s">
-        <v>280</v>
-      </c>
-      <c r="B15" t="s">
-        <v>281</v>
-      </c>
-      <c r="C15">
-        <v>14</v>
-      </c>
-      <c r="D15" t="s">
-        <v>206</v>
-      </c>
-      <c r="E15" t="s">
-        <v>295</v>
-      </c>
-      <c r="F15" t="s">
-        <v>167</v>
-      </c>
-      <c r="G15">
-        <v>30</v>
-      </c>
-      <c r="H15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" t="s">
-        <v>280</v>
-      </c>
-      <c r="B16" t="s">
-        <v>281</v>
-      </c>
-      <c r="C16">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E16" t="s">
-        <v>298</v>
-      </c>
       <c r="F16" t="s">
-        <v>178</v>
-      </c>
-      <c r="G16">
-        <v>15</v>
+        <v>176</v>
+      </c>
+      <c r="G16" t="s">
+        <v>304</v>
       </c>
       <c r="H16" t="s">
         <v>6</v>
       </c>
       <c r="I16" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B17" t="s">
-        <v>281</v>
-      </c>
-      <c r="C17">
-        <v>16</v>
+        <v>287</v>
+      </c>
+      <c r="C17" t="s">
+        <v>338</v>
       </c>
       <c r="D17" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="E17" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="F17" t="s">
-        <v>178</v>
-      </c>
-      <c r="G17">
-        <v>15</v>
+        <v>176</v>
+      </c>
+      <c r="G17" t="s">
+        <v>304</v>
       </c>
       <c r="H17" t="s">
         <v>6</v>
       </c>
       <c r="I17" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Must be a valid Type" errorTitle="Invalid Value" showErrorMessage="1" sqref="E2:E100" type="list">
-      <formula1>"quote,engineering,purchasing,receiving,internal,outside_processing,inspection,shipping"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{AF70A2A1-2ECA-5B78-6E88-11C9D949A328}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30.00390625" customWidth="1"/>
-    <col min="2" max="2" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="3" customFormat="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{317CE428-DAFF-22B8-CEC8-F03EF74696C6}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18.00390625" customWidth="1"/>
-    <col min="2" max="2" width="44.00390625" customWidth="1"/>
-    <col min="3" max="3" width="27.00390625" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2920,7 +3003,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -2931,7 +3014,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -2942,7 +3025,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>114</v>
       </c>
@@ -2953,7 +3036,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>117</v>
       </c>
@@ -2964,7 +3047,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>120</v>
       </c>
@@ -2976,28 +3059,22 @@
       </c>
     </row>
   </sheetData>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{07364AB8-5828-9F08-B798-399B0CC14DFB}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="17.00390625" customWidth="1"/>
-    <col min="2" max="2" width="18.00390625" customWidth="1"/>
-    <col min="3" max="3" width="48.00390625" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -3007,177 +3084,127 @@
       <c r="C1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" t="s">
-        <v>124</v>
       </c>
       <c r="B2" t="s">
         <v>108</v>
       </c>
       <c r="C2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>125</v>
-      </c>
-      <c r="D2" t="str">
-        <f>IF(B2="","",IF(COUNTIF(Teams!A$2:A$6,B2)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" t="s">
-        <v>127</v>
       </c>
       <c r="B3" t="s">
         <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" s="2" t="str">
-        <f>IF(B3="","",IF(COUNTIF(Teams!A$2:A$6,B3)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B4" t="s">
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="2" t="str">
-        <f>IF(B4="","",IF(COUNTIF(Teams!A$2:A$6,B4)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B5" t="s">
         <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="2" t="str">
-        <f>IF(B5="","",IF(COUNTIF(Teams!A$2:A$6,B5)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
         <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6" s="2" t="str">
-        <f>IF(B6="","",IF(COUNTIF(Teams!A$2:A$6,B6)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
         <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="2" t="str">
-        <f>IF(B7="","",IF(COUNTIF(Teams!A$2:A$6,B7)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
         <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="2" t="str">
-        <f>IF(B8="","",IF(COUNTIF(Teams!A$2:A$6,B8)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
         <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" t="str">
-        <f>IF(B9="","",IF(COUNTIF(Teams!A$2:A$6,B9)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s">
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" t="str">
-        <f>IF(B10="","",IF(COUNTIF(Teams!A$2:A$6,B10)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Must match a Team Name from Teams sheet" errorTitle="Invalid Value" showErrorMessage="1" sqref="B2:B100" type="list">
-      <formula1>"Day Shift Team,Night Shift Team,Swing Shift Team,Welding Team,Quality Team"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E3AFAAF2-E7F8-5828-5933-AE8BD08B7618}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12.00390625" customWidth="1"/>
-    <col min="2" max="2" width="20.00390625" customWidth="1"/>
-    <col min="3" max="3" width="14.00390625" customWidth="1"/>
-    <col min="4" max="4" width="21.00390625" customWidth="1"/>
-    <col min="5" max="5" width="22.00390625" customWidth="1"/>
-    <col min="6" max="6" width="23.00390625" customWidth="1"/>
-    <col min="7" max="7" width="17.00390625" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -3191,602 +3218,511 @@
         <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>144</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" t="s">
         <v>145</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>146</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>147</v>
-      </c>
-      <c r="C2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" t="s">
-        <v>149</v>
       </c>
       <c r="E2" t="s">
         <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" t="s">
         <v>150</v>
       </c>
-      <c r="H2" t="str">
-        <f>IF(E2="","",IF(COUNTIF(Teams!A$2:A$6,E2)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" t="s">
-        <v>152</v>
-      </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
         <v>108</v>
       </c>
       <c r="F3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H3" s="2" t="str">
-        <f>IF(E3="","",IF(COUNTIF(Teams!A$2:A$6,E3)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" t="s">
         <v>153</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>154</v>
-      </c>
-      <c r="C4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D4" t="s">
-        <v>156</v>
       </c>
       <c r="E4" t="s">
         <v>111</v>
       </c>
       <c r="F4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G4" t="s">
-        <v>150</v>
-      </c>
-      <c r="H4" s="2" t="str">
-        <f>IF(E4="","",IF(COUNTIF(Teams!A$2:A$6,E4)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" t="s">
         <v>157</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>158</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>159</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B6" t="s">
         <v>160</v>
       </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>137</v>
-      </c>
-      <c r="G5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H5" s="2" t="str">
-        <f>IF(E5="","",IF(COUNTIF(Teams!A$2:A$6,E5)&gt;0,"✓","✗ Not Found"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" t="s">
+      <c r="C6" t="s">
         <v>161</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>162</v>
-      </c>
-      <c r="C6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D6" t="s">
-        <v>164</v>
       </c>
       <c r="E6" t="s">
         <v>117</v>
       </c>
       <c r="F6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
         <v>129</v>
       </c>
-      <c r="G6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H6" s="2" t="str">
-        <f>IF(E6="","",IF(COUNTIF(Teams!A$2:A$6,E6)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" t="s">
+      <c r="G7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" t="s">
         <v>165</v>
       </c>
-      <c r="B7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>131</v>
-      </c>
-      <c r="G7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H7" s="2" t="str">
-        <f>IF(E7="","",IF(COUNTIF(Teams!A$2:A$6,E7)&gt;0,"✓","✗ Not Found"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F8" t="s">
-        <v>137</v>
-      </c>
-      <c r="G8" t="s">
-        <v>150</v>
-      </c>
-      <c r="H8" s="2" t="str">
-        <f>IF(E8="","",IF(COUNTIF(Teams!A$2:A$6,E8)&gt;0,"✓","✗ Not Found"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B9" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" t="s">
-        <v>174</v>
-      </c>
-      <c r="D9" t="s">
-        <v>175</v>
-      </c>
-      <c r="G9" t="s">
-        <v>150</v>
-      </c>
-      <c r="H9" s="2" t="str">
-        <f>IF(E9="","",IF(COUNTIF(Teams!A$2:A$6,E9)&gt;0,"✓","✗ Not Found"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B10" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" t="s">
-        <v>133</v>
-      </c>
-      <c r="G10" t="s">
-        <v>150</v>
-      </c>
-      <c r="H10" s="2" t="str">
-        <f>IF(E10="","",IF(COUNTIF(Teams!A$2:A$6,E10)&gt;0,"✓","✗ Not Found"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" t="s">
+      <c r="D11" t="s">
         <v>179</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>180</v>
       </c>
-      <c r="C11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="B12" t="s">
         <v>181</v>
       </c>
-      <c r="F11" t="s">
-        <v>131</v>
-      </c>
-      <c r="G11" t="s">
-        <v>150</v>
-      </c>
-      <c r="H11" s="2" t="str">
-        <f>IF(E11="","",IF(COUNTIF(Teams!A$2:A$6,E11)&gt;0,"✓","✗ Not Found"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" t="s">
+      <c r="C12" t="s">
         <v>182</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>183</v>
-      </c>
-      <c r="C12" t="s">
-        <v>184</v>
-      </c>
-      <c r="D12" t="s">
-        <v>185</v>
       </c>
       <c r="E12" t="s">
         <v>108</v>
       </c>
       <c r="F12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H12" s="2" t="str">
-        <f>IF(E12="","",IF(COUNTIF(Teams!A$2:A$6,E12)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" t="s">
         <v>186</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
         <v>187</v>
-      </c>
-      <c r="C13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" t="s">
-        <v>189</v>
       </c>
       <c r="E13" t="s">
         <v>108</v>
       </c>
       <c r="F13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" s="2" t="str">
-        <f>IF(E13="","",IF(COUNTIF(Teams!A$2:A$6,E13)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" t="s">
         <v>190</v>
-      </c>
-      <c r="B14" t="s">
-        <v>191</v>
-      </c>
-      <c r="C14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D14" t="s">
-        <v>192</v>
       </c>
       <c r="E14" t="s">
         <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H14" s="2" t="str">
-        <f>IF(E14="","",IF(COUNTIF(Teams!A$2:A$6,E14)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" t="s">
         <v>193</v>
-      </c>
-      <c r="B15" t="s">
-        <v>194</v>
-      </c>
-      <c r="C15" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" t="s">
-        <v>195</v>
       </c>
       <c r="E15" t="s">
         <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G15" t="s">
-        <v>150</v>
-      </c>
-      <c r="H15" s="2" t="str">
-        <f>IF(E15="","",IF(COUNTIF(Teams!A$2:A$6,E15)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" t="s">
         <v>196</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>197</v>
-      </c>
-      <c r="C16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" t="s">
-        <v>199</v>
       </c>
       <c r="E16" t="s">
         <v>108</v>
       </c>
       <c r="F16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G16" t="s">
-        <v>150</v>
-      </c>
-      <c r="H16" s="2" t="str">
-        <f>IF(E16="","",IF(COUNTIF(Teams!A$2:A$6,E16)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" t="s">
+        <v>199</v>
+      </c>
+      <c r="C17" t="s">
         <v>200</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>201</v>
-      </c>
-      <c r="C17" t="s">
-        <v>202</v>
-      </c>
-      <c r="D17" t="s">
-        <v>203</v>
       </c>
       <c r="E17" t="s">
         <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>150</v>
-      </c>
-      <c r="H17" s="2" t="str">
-        <f>IF(E17="","",IF(COUNTIF(Teams!A$2:A$6,E17)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D18" t="s">
         <v>204</v>
-      </c>
-      <c r="B18" t="s">
-        <v>205</v>
-      </c>
-      <c r="C18" t="s">
-        <v>167</v>
-      </c>
-      <c r="D18" t="s">
-        <v>206</v>
       </c>
       <c r="E18" t="s">
         <v>120</v>
       </c>
       <c r="F18" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G18" t="s">
-        <v>150</v>
-      </c>
-      <c r="H18" s="2" t="str">
-        <f>IF(E18="","",IF(COUNTIF(Teams!A$2:A$6,E18)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" t="s">
         <v>207</v>
-      </c>
-      <c r="B19" t="s">
-        <v>208</v>
-      </c>
-      <c r="C19" t="s">
-        <v>155</v>
-      </c>
-      <c r="D19" t="s">
-        <v>209</v>
       </c>
       <c r="E19" t="s">
         <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H19" s="2" t="str">
-        <f>IF(E19="","",IF(COUNTIF(Teams!A$2:A$6,E19)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" t="s">
         <v>210</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>211</v>
-      </c>
-      <c r="C20" t="s">
-        <v>212</v>
-      </c>
-      <c r="D20" t="s">
-        <v>213</v>
       </c>
       <c r="E20" t="s">
         <v>108</v>
       </c>
       <c r="F20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G20" t="s">
-        <v>150</v>
-      </c>
-      <c r="H20" t="str">
-        <f>IF(E20="","",IF(COUNTIF(Teams!A$2:A$6,E20)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation allowBlank="1" error="Must be a valid Work Center Type" errorTitle="Invalid Value" showErrorMessage="1" sqref="D2:D100" type="list">
-      <formula1>"CNC Mill,CNC Lathe,Water Jet,Band Saw,Press Brake,TIG Welding,MIG Welding,Electron Beam Welding,Punch Press,Hardware Installation,Deburr Station,Shipping,Incoming Inspection,Outgoing Inspection,Tool Crib,Quoting,Engineering Review,CAM Programming,Purchasing,Receiving,Final Inspection,Grinding"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must match a Team Name from Teams sheet" errorTitle="Invalid Value" showErrorMessage="1" sqref="E2:E100" type="list">
-      <formula1>"Day Shift Team,Night Shift Team,Swing Shift Team,Welding Team,Quality Team"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must be yes or no" errorTitle="Invalid Value" showErrorMessage="1" sqref="G2:G100" type="list">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must match a Department Name" errorTitle="Invalid Value" showErrorMessage="1" sqref="F2:F100" type="list">
-      <formula1>"Machining,Machining - Night,Fabrication,Quality,Shipping,Assembly,Cutting,Engineering,Admin"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{98FB8BD8-F39A-D2C9-B579-2E1D229090FF}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30.00390625" customWidth="1"/>
-    <col min="2" max="2" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="3" customFormat="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{CC751F68-2B98-1E88-D868-6384B0773578}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27.00390625" customWidth="1"/>
-    <col min="2" max="2" width="15.00390625" customWidth="1"/>
-    <col min="3" max="3" width="12.00390625" customWidth="1"/>
-    <col min="4" max="4" width="21.00390625" customWidth="1"/>
-    <col min="5" max="6" width="22.00390625" customWidth="1"/>
-    <col min="7" max="7" width="23.00390625" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -3797,203 +3733,157 @@
         <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>215</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" t="s">
         <v>216</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>217</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>218</v>
       </c>
-      <c r="C2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D2" t="s">
-        <v>220</v>
-      </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F2" t="s">
         <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H2" t="str">
-        <f>IF(F2="","",IF(COUNTIF(Teams!A$2:A$6,F2)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" t="s">
         <v>221</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>222</v>
       </c>
-      <c r="C3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D3" t="s">
-        <v>224</v>
-      </c>
       <c r="E3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F3" t="s">
         <v>108</v>
       </c>
       <c r="G3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H3" s="2" t="str">
-        <f>IF(F3="","",IF(COUNTIF(Teams!A$2:A$6,F3)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>225</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>226</v>
       </c>
-      <c r="C4" t="s">
-        <v>219</v>
-      </c>
-      <c r="D4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E4" t="s">
-        <v>220</v>
-      </c>
-      <c r="F4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="C5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
         <v>129</v>
       </c>
-      <c r="H4" s="2" t="str">
-        <f>IF(F4="","",IF(COUNTIF(Teams!A$2:A$6,F4)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="2" t="str">
-        <f>IF(F5="","",IF(COUNTIF(Teams!A$2:A$6,F5)&gt;0,"✓","✗ Not Found"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H6" s="2" t="str">
-        <f>IF(F6="","",IF(COUNTIF(Teams!A$2:A$6,F6)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation allowBlank="1" error="Must be a valid App Role" errorTitle="Invalid Value" showErrorMessage="1" sqref="C2:C100" type="list">
-      <formula1>"admin,supervisor,operator,viewer"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must be a valid Org Role" errorTitle="Invalid Value" showErrorMessage="1" sqref="D2:D100" type="list">
-      <formula1>"owner,admin,member"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must be a valid Team Role" errorTitle="Invalid Value" showErrorMessage="1" sqref="E2:E100" type="list">
-      <formula1>"owner,admin,member"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must match a Team Name from Teams sheet" errorTitle="Invalid Value" showErrorMessage="1" sqref="F2:F100" type="list">
-      <formula1>"Day Shift Team,Night Shift Team,Swing Shift Team,Welding Team,Quality Team"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must match a Department Name" errorTitle="Invalid Value" showErrorMessage="1" sqref="G2:G100" type="list">
-      <formula1>"Machining,Machining - Night,Fabrication,Quality,Shipping,Assembly,Cutting,Engineering,Admin"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A3DC7798-42D8-8793-23F8-B9544E3ECB68}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30.00390625" customWidth="1"/>
-    <col min="2" max="2" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="3" customFormat="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -4001,53 +3891,47 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B4" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{242AA028-4C59-9B83-8ED8-F8FC1C254548}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14.00390625" customWidth="1"/>
-    <col min="2" max="4" width="24.00390625" customWidth="1"/>
-    <col min="5" max="5" width="21.00390625" customWidth="1"/>
-    <col min="6" max="6" width="10.00390625" customWidth="1"/>
-    <col min="7" max="7" width="13.00390625" customWidth="1"/>
-    <col min="8" max="8" width="23.00390625" customWidth="1"/>
-    <col min="9" max="9" width="22.00390625" customWidth="1"/>
-    <col min="10" max="10" width="23.00390625" customWidth="1"/>
-    <col min="11" max="11" width="21.00390625" customWidth="1"/>
-    <col min="12" max="12" width="25.00390625" customWidth="1"/>
-    <col min="13" max="13" width="36.00390625" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="25" customWidth="1"/>
+    <col min="13" max="13" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -4055,13 +3939,13 @@
         <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>61</v>
@@ -4070,94 +3954,80 @@
         <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>87</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>240</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>241</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>242</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>243</v>
       </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-      <c r="F2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G2" t="s">
-        <v>245</v>
-      </c>
       <c r="H2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I2" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K2" t="s">
+        <v>245</v>
+      </c>
+      <c r="L2" t="s">
         <v>246</v>
       </c>
-      <c r="K2">
-        <v>120</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>247</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>248</v>
       </c>
-      <c r="N2" t="str">
-        <f>IF(I2="","",IF(COUNTIF(Teams!A$2:A$6,I2)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-      <c r="O2" t="str">
-        <f>IF(H2="","",IF(COUNTIF(Stations!A$2:A$19,H2)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>249</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>250</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>251</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>252</v>
-      </c>
-      <c r="E3">
-        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>253</v>
@@ -4166,102 +4036,86 @@
         <v>254</v>
       </c>
       <c r="H3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I3" t="s">
         <v>111</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" t="s">
         <v>255</v>
       </c>
-      <c r="K3">
-        <v>240</v>
+      <c r="K3" t="s">
+        <v>256</v>
       </c>
       <c r="L3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M3" t="s">
-        <v>257</v>
-      </c>
-      <c r="N3" s="2" t="str">
-        <f>IF(I3="","",IF(COUNTIF(Teams!A$2:A$6,I3)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-      <c r="O3" s="2" t="str">
-        <f>IF(H3="","",IF(COUNTIF(Stations!A$2:A$19,H3)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
+        <v>262</v>
+      </c>
+      <c r="E4" t="s">
+        <v>263</v>
       </c>
       <c r="F4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I4" t="s">
         <v>120</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="K4">
-        <v>60</v>
+      <c r="J4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K4" t="s">
+        <v>265</v>
       </c>
       <c r="L4" t="s">
         <v>6</v>
       </c>
       <c r="M4" t="s">
-        <v>263</v>
-      </c>
-      <c r="N4" s="2" t="str">
-        <f>IF(I4="","",IF(COUNTIF(Teams!A$2:A$6,I4)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-      <c r="O4" s="2" t="str">
-        <f>IF(H4="","",IF(COUNTIF(Stations!A$2:A$19,H4)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
+        <v>270</v>
+      </c>
+      <c r="E5" t="s">
+        <v>240</v>
       </c>
       <c r="F5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H5" t="s">
         <v>6</v>
@@ -4269,120 +4123,84 @@
       <c r="I5" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="K5">
-        <v>180</v>
+      <c r="J5" t="s">
+        <v>272</v>
+      </c>
+      <c r="K5" t="s">
+        <v>273</v>
       </c>
       <c r="L5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M5" t="s">
-        <v>271</v>
-      </c>
-      <c r="N5" s="2" t="str">
-        <f>IF(I5="","",IF(COUNTIF(Teams!A$2:A$6,I5)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-      <c r="O5" s="2" t="str">
-        <f>IF(H5="","",IF(COUNTIF(Stations!A$2:A$19,H5)&gt;0,"✓","✗ Not Found"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
+        <v>240</v>
+      </c>
+      <c r="E6" t="s">
+        <v>279</v>
       </c>
       <c r="F6" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I6" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="K6">
-        <v>480</v>
+      <c r="J6" t="s">
+        <v>282</v>
+      </c>
+      <c r="K6" t="s">
+        <v>283</v>
       </c>
       <c r="L6" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="M6" t="s">
-        <v>279</v>
-      </c>
-      <c r="N6" s="2" t="str">
-        <f>IF(I6="","",IF(COUNTIF(Teams!A$2:A$6,I6)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
-      </c>
-      <c r="O6" s="2" t="str">
-        <f>IF(H6="","",IF(COUNTIF(Stations!A$2:A$19,H6)&gt;0,"✓","✗ Not Found"))</f>
-        <v>✓</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation allowBlank="1" error="Must be a valid Priority" errorTitle="Invalid Value" showErrorMessage="1" sqref="F2:F100" type="list">
-      <formula1>"low,normal,high,urgent,critical"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must be a valid Status" errorTitle="Invalid Value" showErrorMessage="1" sqref="G2:G100" type="list">
-      <formula1>"pending,queued,in_progress,on_hold"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must match a Team Name" errorTitle="Invalid Value" showErrorMessage="1" sqref="I2:I100" type="list">
-      <formula1>"Day Shift Team,Night Shift Team,Swing Shift Team,Welding Team,Quality Team"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" error="Must match a Station ID" errorTitle="Invalid Value" showErrorMessage="1" sqref="H2:H100" type="list">
-      <formula1>"CNC-001,CNC-002,LATHE-001,WJ-001,WELD-001,INSP-001,SAW-001,DEB-001,PKG-001,CMM-001,QUOTE-001,ENG-001,CAM-001,PUR-001,REC-001,TOOL-001,FINSP-001,GRIND-001,ASSY-001"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9D5E5098-1958-336C-21B8-8E70A4DA9BD7}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV10000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30.00390625" customWidth="1"/>
-    <col min="2" max="2" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="3" customFormat="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -4390,7 +4208,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -4399,13 +4217,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>